--- a/data/trans_dic/P16A08-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A08-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,19</t>
+          <t>0,97; 5,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,47</t>
+          <t>2,03; 7,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,7</t>
+          <t>2,03; 6,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 12,2</t>
+          <t>3,26; 12,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,73</t>
+          <t>0,4; 3,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,12; 10,61</t>
+          <t>4,36; 10,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 8,02</t>
+          <t>2,53; 7,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,3</t>
+          <t>0,96; 3,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,66</t>
+          <t>1,03; 3,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,73</t>
+          <t>3,48; 7,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,14</t>
+          <t>2,64; 5,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,4</t>
+          <t>2,58; 7,63</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,09</t>
+          <t>1,17; 4,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 9,51</t>
+          <t>4,34; 9,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,54</t>
+          <t>1,6; 4,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,93</t>
+          <t>2,83; 7,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 8,89</t>
+          <t>4,43; 8,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,61</t>
+          <t>5,14; 9,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 9,36</t>
+          <t>5,07; 9,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 7,39</t>
+          <t>3,77; 7,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 5,64</t>
+          <t>3,1; 5,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,78</t>
+          <t>5,27; 8,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 6,41</t>
+          <t>3,47; 6,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 6,79</t>
+          <t>3,7; 6,77</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,18</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,23</t>
+          <t>0,89; 4,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 5,24</t>
+          <t>1,42; 5,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 6,55</t>
+          <t>1,21; 6,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,63</t>
+          <t>1,38; 4,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 10,38</t>
+          <t>4,54; 10,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,2</t>
+          <t>1,42; 5,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,0</t>
+          <t>1,15; 4,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,01</t>
+          <t>0,98; 3,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,71</t>
+          <t>3,36; 6,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,48</t>
+          <t>1,8; 4,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,3</t>
+          <t>1,56; 4,31</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,05</t>
+          <t>1,22; 5,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,88</t>
+          <t>0,84; 4,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,33</t>
+          <t>2,45; 7,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,5</t>
+          <t>0,6; 4,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,81</t>
+          <t>1,95; 6,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,4</t>
+          <t>2,34; 6,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 9,45</t>
+          <t>4,15; 9,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 47,19</t>
+          <t>2,04; 48,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,61</t>
+          <t>2,01; 4,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,34</t>
+          <t>1,99; 4,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,51</t>
+          <t>3,9; 7,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 35,77</t>
+          <t>1,95; 36,02</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,72</t>
+          <t>1,4; 6,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 7,31</t>
+          <t>1,85; 7,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,69</t>
+          <t>0,75; 4,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 7,47</t>
+          <t>1,62; 7,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,93; 12,96</t>
+          <t>5,15; 13,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,07; 14,11</t>
+          <t>6,2; 14,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,74</t>
+          <t>2,53; 7,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 6,33</t>
+          <t>2,29; 6,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,89; 8,99</t>
+          <t>3,84; 8,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,77; 9,81</t>
+          <t>4,8; 9,48</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,32</t>
+          <t>2,07; 5,52</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,71</t>
+          <t>2,46; 5,71</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,3</t>
+          <t>0,38; 4,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 7,38</t>
+          <t>1,85; 6,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,7</t>
+          <t>1,87; 6,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,23</t>
+          <t>1,14; 4,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,06</t>
+          <t>1,63; 6,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 8,37</t>
+          <t>2,88; 8,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 8,22</t>
+          <t>2,32; 8,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 6,65</t>
+          <t>2,0; 6,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,34</t>
+          <t>1,47; 4,53</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,47</t>
+          <t>2,71; 6,6</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,5</t>
+          <t>2,75; 6,27</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,01</t>
+          <t>1,92; 4,81</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,97</t>
+          <t>0,72; 2,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,71</t>
+          <t>0,77; 2,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,8</t>
+          <t>1,21; 4,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,19</t>
+          <t>1,62; 4,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,6</t>
+          <t>1,7; 4,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,9</t>
+          <t>2,63; 5,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,84</t>
+          <t>4,04; 7,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 8,03</t>
+          <t>2,69; 7,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,28</t>
+          <t>1,5; 3,22</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,92</t>
+          <t>1,98; 3,8</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 5,35</t>
+          <t>2,96; 5,18</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,68</t>
+          <t>2,66; 5,74</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,39</t>
+          <t>2,67; 5,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,38</t>
+          <t>2,36; 5,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,65</t>
+          <t>2,06; 4,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,08</t>
+          <t>0,91; 4,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,24</t>
+          <t>2,62; 5,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,7</t>
+          <t>3,01; 5,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,74; 6,96</t>
+          <t>3,67; 6,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,64</t>
+          <t>4,7; 7,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,75</t>
+          <t>2,82; 4,9</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,16</t>
+          <t>3,13; 5,19</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,21; 5,25</t>
+          <t>3,27; 5,29</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,2</t>
+          <t>2,48; 5,19</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,01</t>
+          <t>1,86; 2,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,12</t>
+          <t>2,78; 4,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,7</t>
+          <t>2,51; 3,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,14</t>
+          <t>2,42; 4,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,28; 4,59</t>
+          <t>3,27; 4,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,78; 6,35</t>
+          <t>4,74; 6,34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,2</t>
+          <t>4,68; 6,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,18; 12,66</t>
+          <t>4,21; 13,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,64</t>
+          <t>2,74; 3,65</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,95; 5,02</t>
+          <t>4,02; 5,06</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,74; 4,77</t>
+          <t>3,78; 4,78</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,79</t>
+          <t>3,7; 8,08</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2681; 14174</t>
+          <t>2653; 14709</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5143; 18787</t>
+          <t>5898; 20737</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5884; 19668</t>
+          <t>5954; 19996</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10989; 38006</t>
+          <t>10152; 38187</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1022; 9742</t>
+          <t>1055; 10298</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11536; 29735</t>
+          <t>12222; 29582</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6987; 23154</t>
+          <t>7290; 22606</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2732; 9561</t>
+          <t>2787; 10159</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5585; 19516</t>
+          <t>5480; 18885</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20427; 44130</t>
+          <t>19855; 43932</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16142; 35734</t>
+          <t>15374; 34675</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14752; 44483</t>
+          <t>15524; 45840</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5728; 20174</t>
+          <t>5749; 19830</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20904; 48061</t>
+          <t>21954; 49227</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8152; 22829</t>
+          <t>8044; 23129</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13952; 41021</t>
+          <t>14654; 40356</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21783; 44799</t>
+          <t>22341; 42885</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26308; 50252</t>
+          <t>26893; 51351</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25675; 48985</t>
+          <t>26537; 49880</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19846; 37941</t>
+          <t>19361; 37288</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31288; 56274</t>
+          <t>30940; 57949</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53945; 90318</t>
+          <t>54225; 89346</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37211; 65704</t>
+          <t>35591; 63711</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38211; 70008</t>
+          <t>38119; 69819</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 10143</t>
+          <t>0; 9453</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2825; 13657</t>
+          <t>2886; 13139</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4378; 16702</t>
+          <t>4536; 17074</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4041; 20658</t>
+          <t>3810; 19861</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3889; 15529</t>
+          <t>4645; 16146</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16433; 35401</t>
+          <t>15488; 36524</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5456; 17476</t>
+          <t>4771; 16972</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4315; 13978</t>
+          <t>4012; 14386</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5684; 19692</t>
+          <t>6404; 19879</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21166; 44588</t>
+          <t>22300; 44558</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12156; 29363</t>
+          <t>11793; 29246</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10467; 28563</t>
+          <t>10380; 28674</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4217; 18127</t>
+          <t>4359; 18327</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2995; 14501</t>
+          <t>3141; 15190</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8834; 27108</t>
+          <t>9054; 26125</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1345; 14075</t>
+          <t>1886; 14908</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7472; 21598</t>
+          <t>7252; 22813</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8740; 24813</t>
+          <t>9078; 25700</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16051; 36586</t>
+          <t>16091; 38418</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9768; 224331</t>
+          <t>9707; 229299</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13632; 33693</t>
+          <t>14661; 33046</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15061; 33045</t>
+          <t>15153; 33433</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29050; 56840</t>
+          <t>29498; 56884</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14893; 281863</t>
+          <t>15399; 283787</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2691; 13660</t>
+          <t>2849; 13164</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4122; 15539</t>
+          <t>3928; 15943</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1591; 9903</t>
+          <t>1590; 10102</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2782; 13352</t>
+          <t>2898; 13189</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10246; 26912</t>
+          <t>10695; 28453</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13326; 30993</t>
+          <t>13605; 30933</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5308; 16913</t>
+          <t>5527; 17398</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5083; 13208</t>
+          <t>4788; 13275</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15972; 36955</t>
+          <t>15773; 36534</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20620; 42417</t>
+          <t>20749; 40957</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8405; 22884</t>
+          <t>8902; 23732</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9644; 22122</t>
+          <t>9524; 22139</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1610; 11653</t>
+          <t>1030; 12141</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5040; 20216</t>
+          <t>5073; 18332</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4915; 17623</t>
+          <t>4929; 16761</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2773; 14102</t>
+          <t>3068; 13423</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4401; 16844</t>
+          <t>4539; 17045</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7996; 23272</t>
+          <t>8017; 24093</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7197; 22442</t>
+          <t>6342; 22506</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5297; 17088</t>
+          <t>5153; 16797</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7771; 23833</t>
+          <t>8082; 24870</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15975; 35716</t>
+          <t>14940; 36462</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14596; 34874</t>
+          <t>14744; 33605</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9731; 26370</t>
+          <t>10093; 25357</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4365; 18250</t>
+          <t>4442; 17608</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4933; 17955</t>
+          <t>5124; 18891</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7513; 24967</t>
+          <t>7970; 26379</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9982; 26179</t>
+          <t>10093; 27916</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11616; 29380</t>
+          <t>10859; 27820</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18868; 40968</t>
+          <t>18263; 41366</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27643; 54169</t>
+          <t>27939; 53164</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>23106; 68156</t>
+          <t>22817; 67656</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>19842; 41044</t>
+          <t>18816; 40368</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27311; 53232</t>
+          <t>26870; 51554</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40207; 72111</t>
+          <t>39864; 69779</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>39493; 83756</t>
+          <t>39128; 84593</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>19041; 40046</t>
+          <t>19814; 41240</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>20045; 41763</t>
+          <t>18369; 41161</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16710; 36184</t>
+          <t>16023; 35707</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8496; 37886</t>
+          <t>8471; 37674</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>20445; 41082</t>
+          <t>20523; 40593</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23933; 46825</t>
+          <t>24729; 47670</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30857; 57536</t>
+          <t>30303; 56474</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>33518; 54626</t>
+          <t>33611; 53875</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>43403; 72510</t>
+          <t>43007; 74820</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>48846; 82510</t>
+          <t>49958; 82977</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>51457; 84283</t>
+          <t>52541; 84961</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>39468; 85434</t>
+          <t>40817; 85276</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>61545; 98468</t>
+          <t>61076; 96429</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>97114; 140864</t>
+          <t>94908; 139426</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>85287; 125454</t>
+          <t>85196; 126112</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>84475; 143314</t>
+          <t>83532; 141710</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>110742; 154949</t>
+          <t>110391; 157218</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>169425; 224957</t>
+          <t>167870; 224586</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>163880; 219774</t>
+          <t>165895; 218225</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>152869; 463207</t>
+          <t>153989; 503983</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>180513; 242450</t>
+          <t>182254; 242954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>274781; 349313</t>
+          <t>279694; 352409</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>259786; 330773</t>
+          <t>262087; 332000</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>261143; 625379</t>
+          <t>263416; 574729</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A08-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A08-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,39</t>
+          <t>0,96; 5,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,15</t>
+          <t>1,79; 6,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,81</t>
+          <t>2,01; 6,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 12,26</t>
+          <t>3,08; 9,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,95</t>
+          <t>0,41; 3,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 10,55</t>
+          <t>4,35; 11,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,83</t>
+          <t>2,48; 7,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,51</t>
+          <t>1,52; 5,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,54</t>
+          <t>0,92; 3,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 7,7</t>
+          <t>3,53; 7,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,95</t>
+          <t>2,71; 6,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,63</t>
+          <t>2,57; 6,23</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,02</t>
+          <t>1,19; 4,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 9,74</t>
+          <t>4,1; 9,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,6</t>
+          <t>1,59; 4,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 7,8</t>
+          <t>2,7; 7,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 8,51</t>
+          <t>4,49; 8,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,14; 9,82</t>
+          <t>5,18; 10,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 9,54</t>
+          <t>4,97; 9,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,77; 7,26</t>
+          <t>3,93; 7,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,81</t>
+          <t>3,13; 5,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 8,69</t>
+          <t>5,33; 8,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,21</t>
+          <t>3,74; 6,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 6,77</t>
+          <t>3,61; 6,54</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,96</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,07</t>
+          <t>0,89; 4,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,36</t>
+          <t>1,44; 5,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,29</t>
+          <t>1,36; 5,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,81</t>
+          <t>1,18; 4,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,54; 10,71</t>
+          <t>4,58; 10,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,05</t>
+          <t>1,62; 5,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,12</t>
+          <t>1,26; 3,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,04</t>
+          <t>0,85; 2,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,71</t>
+          <t>3,33; 6,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,47</t>
+          <t>1,75; 4,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,31</t>
+          <t>1,66; 4,05</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,11</t>
+          <t>1,21; 5,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,06</t>
+          <t>0,83; 3,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,06</t>
+          <t>2,46; 6,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,77</t>
+          <t>0,69; 4,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,14</t>
+          <t>1,88; 5,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,62</t>
+          <t>2,47; 6,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 9,92</t>
+          <t>4,11; 9,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 48,23</t>
+          <t>1,67; 5,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,53</t>
+          <t>1,97; 4,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,39</t>
+          <t>1,98; 4,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,51</t>
+          <t>3,76; 7,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 36,02</t>
+          <t>1,56; 4,1</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,48</t>
+          <t>1,43; 6,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,5</t>
+          <t>1,9; 7,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,78</t>
+          <t>0,81; 4,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 7,38</t>
+          <t>1,4; 6,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,15; 13,7</t>
+          <t>5,02; 13,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 14,09</t>
+          <t>6,08; 14,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,96</t>
+          <t>2,57; 8,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,36</t>
+          <t>2,38; 6,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,84; 8,89</t>
+          <t>3,75; 8,82</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 9,48</t>
+          <t>4,82; 9,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,52</t>
+          <t>2,09; 5,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,71</t>
+          <t>2,3; 5,56</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,48</t>
+          <t>0,38; 4,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,69</t>
+          <t>1,89; 6,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,37</t>
+          <t>1,79; 6,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,98</t>
+          <t>1,1; 5,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,13</t>
+          <t>1,76; 6,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 8,66</t>
+          <t>2,9; 8,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,32; 8,24</t>
+          <t>2,59; 8,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,53</t>
+          <t>1,97; 6,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,53</t>
+          <t>1,57; 4,63</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,6</t>
+          <t>2,89; 6,7</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,27</t>
+          <t>2,79; 6,47</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,81</t>
+          <t>1,92; 4,86</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,86</t>
+          <t>0,71; 2,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,85</t>
+          <t>0,65; 2,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,02</t>
+          <t>1,21; 3,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,47</t>
+          <t>1,93; 4,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,36</t>
+          <t>1,77; 4,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,96</t>
+          <t>2,76; 5,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,69</t>
+          <t>4,09; 7,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,97</t>
+          <t>5,78; 9,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,22</t>
+          <t>1,48; 3,28</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,8</t>
+          <t>2,06; 3,93</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,96; 5,18</t>
+          <t>3,09; 5,5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,74</t>
+          <t>4,22; 6,62</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,55</t>
+          <t>2,54; 5,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,3</t>
+          <t>2,5; 5,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,59</t>
+          <t>2,15; 4,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,06</t>
+          <t>2,17; 4,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,18</t>
+          <t>2,59; 5,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,8</t>
+          <t>2,9; 5,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,67; 6,84</t>
+          <t>3,62; 6,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,7; 7,54</t>
+          <t>4,87; 7,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,82; 4,9</t>
+          <t>2,85; 4,96</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,19</t>
+          <t>3,06; 4,98</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,29</t>
+          <t>3,22; 5,29</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,19</t>
+          <t>3,85; 5,83</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,86; 2,94</t>
+          <t>1,89; 2,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,08</t>
+          <t>2,78; 4,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,72</t>
+          <t>2,57; 3,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,1</t>
+          <t>2,82; 4,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,27; 4,65</t>
+          <t>3,32; 4,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,34</t>
+          <t>4,72; 6,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,68; 6,16</t>
+          <t>4,62; 6,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,21; 13,78</t>
+          <t>4,36; 5,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,74; 3,65</t>
+          <t>2,73; 3,58</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,02; 5,06</t>
+          <t>3,99; 5,0</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,78; 4,78</t>
+          <t>3,77; 4,72</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,7; 8,08</t>
+          <t>3,77; 4,68</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19803</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>9213</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25256</t>
+          <t>25753</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2653; 14709</t>
+          <t>2609; 14116</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5898; 20737</t>
+          <t>5192; 18931</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5954; 19996</t>
+          <t>5900; 19712</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10152; 38187</t>
+          <t>9826; 29447</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1055; 10298</t>
+          <t>1059; 9337</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12222; 29582</t>
+          <t>12203; 31770</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7290; 22606</t>
+          <t>7161; 22590</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2787; 10159</t>
+          <t>4820; 18873</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5480; 18885</t>
+          <t>4927; 19791</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19855; 43932</t>
+          <t>20118; 43185</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15374; 34675</t>
+          <t>15801; 35985</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15524; 45840</t>
+          <t>16348; 39527</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24436</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27328</t>
+          <t>28887</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51764</t>
+          <t>53199</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5749; 19830</t>
+          <t>5855; 20230</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21954; 49227</t>
+          <t>20731; 46933</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8044; 23129</t>
+          <t>8008; 22513</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14654; 40356</t>
+          <t>14317; 39430</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22341; 42885</t>
+          <t>22611; 44496</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26893; 51351</t>
+          <t>27102; 52375</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26537; 49880</t>
+          <t>25976; 50149</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19361; 37288</t>
+          <t>21410; 39955</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30940; 57949</t>
+          <t>31180; 55924</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>54225; 89346</t>
+          <t>54836; 91965</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35591; 63711</t>
+          <t>38326; 66051</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38119; 69819</t>
+          <t>38849; 70272</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>17609</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 9453</t>
+          <t>0; 9343</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2886; 13139</t>
+          <t>2871; 13881</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4536; 17074</t>
+          <t>4595; 17150</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3810; 19861</t>
+          <t>4292; 18466</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4645; 16146</t>
+          <t>3970; 16428</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15488; 36524</t>
+          <t>15603; 34599</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4771; 16972</t>
+          <t>5461; 17530</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4012; 14386</t>
+          <t>4487; 13793</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6404; 19879</t>
+          <t>5590; 18743</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22300; 44558</t>
+          <t>22098; 45357</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11793; 29246</t>
+          <t>11486; 29052</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10380; 28674</t>
+          <t>11126; 27219</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>7617</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>80245</t>
+          <t>12452</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85930</t>
+          <t>20069</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4359; 18327</t>
+          <t>4325; 18369</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3141; 15190</t>
+          <t>3113; 13832</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9054; 26125</t>
+          <t>9094; 24761</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1886; 14908</t>
+          <t>2583; 18597</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7252; 22813</t>
+          <t>6991; 20785</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9078; 25700</t>
+          <t>9581; 25156</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16091; 38418</t>
+          <t>15922; 37614</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9707; 229299</t>
+          <t>7047; 23615</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14661; 33046</t>
+          <t>14364; 34700</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15153; 33433</t>
+          <t>15101; 33572</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29498; 56884</t>
+          <t>28441; 56004</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15399; 283787</t>
+          <t>12396; 32551</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>15443</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2849; 13164</t>
+          <t>2907; 13652</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3928; 15943</t>
+          <t>4035; 15433</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1590; 10102</t>
+          <t>1702; 9979</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2898; 13189</t>
+          <t>2870; 13011</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10695; 28453</t>
+          <t>10426; 28329</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13605; 30933</t>
+          <t>13352; 31486</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5527; 17398</t>
+          <t>5613; 18383</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4788; 13275</t>
+          <t>5399; 14179</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15773; 36534</t>
+          <t>15418; 36232</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20749; 40957</t>
+          <t>20817; 41129</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8902; 23732</t>
+          <t>8963; 24094</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9524; 22139</t>
+          <t>9974; 24074</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16471</t>
+          <t>16531</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1030; 12141</t>
+          <t>1030; 11617</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5073; 18332</t>
+          <t>5168; 18095</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4929; 16761</t>
+          <t>4710; 16347</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3068; 13423</t>
+          <t>2984; 13922</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4539; 17045</t>
+          <t>4885; 17608</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8017; 24093</t>
+          <t>8073; 24468</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6342; 22506</t>
+          <t>7077; 24021</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5153; 16797</t>
+          <t>5183; 16468</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8082; 24870</t>
+          <t>8636; 25439</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14940; 36462</t>
+          <t>15970; 37000</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14744; 33605</t>
+          <t>14964; 34712</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10093; 25357</t>
+          <t>10276; 25989</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>22072</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>47364</t>
+          <t>56657</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>64168</t>
+          <t>78728</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4442; 17608</t>
+          <t>4383; 17958</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5124; 18891</t>
+          <t>4292; 18872</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7970; 26379</t>
+          <t>7920; 25656</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10093; 27916</t>
+          <t>13880; 34478</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10859; 27820</t>
+          <t>11316; 28683</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18263; 41366</t>
+          <t>19161; 41011</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27939; 53164</t>
+          <t>28264; 52761</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>22817; 67656</t>
+          <t>44613; 72474</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18816; 40368</t>
+          <t>18556; 41060</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26870; 51554</t>
+          <t>27901; 53360</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39864; 69779</t>
+          <t>41683; 74126</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>39128; 84593</t>
+          <t>62975; 98791</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23284</t>
+          <t>26130</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>43461</t>
+          <t>51004</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>66745</t>
+          <t>77134</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>19814; 41240</t>
+          <t>18902; 40904</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>18369; 41161</t>
+          <t>19387; 41807</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16023; 35707</t>
+          <t>16717; 36074</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8471; 37674</t>
+          <t>17283; 39107</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>20523; 40593</t>
+          <t>20254; 41447</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>24729; 47670</t>
+          <t>23804; 48687</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30303; 56474</t>
+          <t>29948; 56124</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>33611; 53875</t>
+          <t>40406; 65868</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>43007; 74820</t>
+          <t>43479; 75770</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>49958; 82977</t>
+          <t>48846; 79654</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>52541; 84961</t>
+          <t>51612; 84919</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>40817; 85276</t>
+          <t>62619; 94861</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>112679</t>
+          <t>119545</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>229682</t>
+          <t>184921</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>342361</t>
+          <t>304467</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>61076; 96429</t>
+          <t>61806; 97361</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>94908; 139426</t>
+          <t>95064; 139924</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>85196; 126112</t>
+          <t>87399; 125072</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>83532; 141710</t>
+          <t>99673; 146731</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>110391; 157218</t>
+          <t>112128; 156802</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>167870; 224586</t>
+          <t>167255; 223801</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>165895; 218225</t>
+          <t>163853; 221970</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>153989; 503983</t>
+          <t>162551; 211185</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>182254; 242954</t>
+          <t>181916; 238183</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>279694; 352409</t>
+          <t>278194; 348033</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>262087; 332000</t>
+          <t>261314; 327835</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>263416; 574729</t>
+          <t>273514; 339927</t>
         </is>
       </c>
     </row>
